--- a/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_65322_completo.xlsx
+++ b/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_65322_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd4ca82062a334d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6ac505572f0c443a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8488</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8258</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8342</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_65322_completo.xlsx
+++ b/49844_Cuenca_Mayo/_raw_reportes_xlsx/IDConfig_65322_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R6ac505572f0c443a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7f94523c7ddd4791"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,651 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7942</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8067</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8162</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7808</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1096</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8008</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8371</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8088</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0524</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9004</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9333</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.2613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.5613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8809</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8163</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8287</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8400</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8546</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8861</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8800</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8213</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8417</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8492</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8550</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8588</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8404</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0346</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.3354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9338</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8167</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8371</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
